--- a/AAII_Financials/Quarterly/LYG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LYG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="92">
   <si>
     <t>LYG</t>
   </si>
@@ -656,281 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="29" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="30" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6793200</v>
+      </c>
+      <c r="E8" s="3">
         <v>6457100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6721400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6302900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6246100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5665400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5467200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5936200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5617600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5470000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6819700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5387700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5182300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5648800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13405400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>9748300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>8508700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>7803800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>7885200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>9873400</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>11540400</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>11533400</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>10985000</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>10383800</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>10623600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3918100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10253200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3111600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10720000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2149000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1051,53 +1057,56 @@
       <c r="AP9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6793200</v>
+      </c>
+      <c r="E10" s="3">
         <v>6457100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6721400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6302900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6246100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5665400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5467200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5936200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5617600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5470000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6819700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5387700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5182300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5648800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1173,8 +1182,11 @@
       <c r="AP10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1217,8 +1229,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1339,8 +1352,11 @@
       <c r="AP12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1461,52 +1477,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>61900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-12100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>50100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-20100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>731100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-30500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>31800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1583,130 +1602,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1185500</v>
+      </c>
+      <c r="E15" s="3">
         <v>668500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>681400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>674400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1197400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>648300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>628200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>558900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1077400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>526700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>531200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>407900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>847000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>413500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1556300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-107600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-1587800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-116600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-2004900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-137700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-1482300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-173400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-1562500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-253700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-1822400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-298200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-1852000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-365100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-1787900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-291600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-1571700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-288200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-1570800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-325800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-1616000</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-1475200</v>
       </c>
-      <c r="AN15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="3">
         <v>-1598600</v>
       </c>
-      <c r="AP15" s="3" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1746,252 +1771,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3738900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3783200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3990600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4736900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3511400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3705500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4385500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3512900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3455200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3413800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3827600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3150900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3104500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2852800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5868200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3">
         <v>2326500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="3">
         <v>1350900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17" s="3">
         <v>1726800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="3">
         <v>3355800</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB17" s="3">
         <v>6318500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD17" s="3">
         <v>4961500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="3">
         <v>5958300</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="3">
         <v>1861000</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>3207500</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="3">
         <v>3808600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>336500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3732900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>139600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5866300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>417400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3054300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2674000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2730800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1566000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2734600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1960000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1081700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2423300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2162300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2056100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2992100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2236800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2077700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2795900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7537300</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>7421800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>7157700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>6077000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>4529400</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3554900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>6578900</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5575200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>9124000</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>7176400</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>6815000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3581600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6520200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2972000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4853700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1731600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2034,8 +2066,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2078,131 +2111,134 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-5394500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-3289700</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3359600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1420300</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2388300</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-4339700</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-4538700</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-5369000</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-3146700</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-3252900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1036900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3202100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1254900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2504500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-663700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4239800</v>
+      </c>
+      <c r="E21" s="3">
         <v>3342400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3412200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2240400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3932000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2608200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1709800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2982200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3239700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2582800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3523200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2644700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2924700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3209400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2212,74 +2248,77 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>5803000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>3703700</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>2116600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5766000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>3722000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5600500</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>3702900</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>4793300</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="3">
         <v>2412400</v>
       </c>
-      <c r="AP21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2322,8 +2361,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2400,252 +2439,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3009200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2674000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2668900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1578100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2722300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1960000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1031600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2443400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2143400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2056100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2260900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2267300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2046000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2795900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2142800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>755800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4132100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2013500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3798100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2517600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4656800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2223100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2141100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1263800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-784800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>98500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2040200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>70800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3978100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2134200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3755000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2237800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4029700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2071100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3562100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2544700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3318200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1717100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2349200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1067900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>928800</v>
+      </c>
+      <c r="E24" s="3">
         <v>620600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>737600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>532300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>790500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>494800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>155200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>656700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>590200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>521600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>689100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>534500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>491800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>765800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>206000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>107600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>921200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>519800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1238200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>532300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>47700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>586800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>538800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>424500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-809500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-540400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>975100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>407600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>922800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>536600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>863800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>485300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1034200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>557200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1073400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>627400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1180400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>545200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1484000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>779500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2766,252 +2814,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2080400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2053300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1931400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1045800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1931800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1465100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>876300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1786600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1553200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1534500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1571800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1732800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1554200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2030100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1936800</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T26" s="3">
         <v>3211000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="3">
         <v>2559900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="3">
         <v>4609100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1602300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB26" s="3">
         <v>24800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD26" s="3">
         <v>1065100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="3">
         <v>3055300</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="3">
         <v>2891200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>2995400</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="3">
         <v>2488600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1917300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2137800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1171900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>865100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>288400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1888000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1865800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1755000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>830700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1737200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1299800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>711100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1621800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1359800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1350100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1392200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1547400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1349600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1868100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1573300</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T27" s="3">
         <v>2873700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="3">
         <v>2210200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="3">
         <v>4306200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1287300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-305000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="3">
         <v>705100</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="3">
         <v>2666700</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="3">
         <v>2583500</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>2747200</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="3">
         <v>2222500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1777800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1878200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1008700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>607000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3132,8 +3189,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3254,8 +3314,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3376,8 +3439,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3498,8 +3564,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3542,208 +3611,214 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>5394500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>3289700</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>3359600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>1420300</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2388300</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>4339700</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>4538700</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1597000</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>5369000</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>3146700</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>3252900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1036900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3202100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1254900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2504500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>663700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2035300</v>
+      </c>
+      <c r="E33" s="3">
         <v>2021600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1886900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>992000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1915300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1448300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>863800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1765200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1699800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1350100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1562900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1715800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1673600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1868100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1573300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T33" s="3">
         <v>2873700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" s="3">
         <v>2210200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="3">
         <v>4306200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1287300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-305000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD33" s="3">
         <v>705100</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="3">
         <v>2666700</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="3">
         <v>2583500</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>2747200</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="3">
         <v>2222500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1777800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1878200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1008700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>607000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3864,257 +3939,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2035300</v>
+      </c>
+      <c r="E35" s="3">
         <v>2021600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1886900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>992000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1915300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1448300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>863800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1765200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1699800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1350100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1562900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1715800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1673600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1868100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1573300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T35" s="3">
         <v>2873700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="3">
         <v>2210200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="3">
         <v>4306200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1287300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-305000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD35" s="3">
         <v>705100</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="3">
         <v>2666700</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH35" s="3">
         <v>2583500</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>2747200</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL35" s="3">
         <v>2222500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1777800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1878200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1008700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>607000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4157,8 +4241,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4201,296 +4286,303 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>81618700</v>
+      </c>
+      <c r="E41" s="3">
         <v>82038300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76210000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83133000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87991500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>81255600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78475700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79151600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84431400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>97034700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>106778900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121388700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>122388400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>134188200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>111328400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>124350600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
         <v>105905700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>85457600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>107254300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z41" s="3">
         <v>98742900</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB41" s="3">
         <v>116895500</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3">
         <v>88943700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="3">
         <v>91120800</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH41" s="3">
         <v>81351400</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>97379600</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL41" s="3">
         <v>85937100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>64916800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>78533800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>74347300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>98838300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>92293800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>143640700</v>
+      </c>
+      <c r="E42" s="3">
         <v>344554700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154127900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>337813500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>139408100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>305120200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>148820100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>379786900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>127720000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>131550900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>325264200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>112730800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>73561200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>91352700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>45820700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>113177300</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V42" s="3">
         <v>97333700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>28775400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>26465400</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z42" s="3">
         <v>34685700</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB42" s="3">
         <v>42989800</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD42" s="3">
         <v>35961800</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="3">
         <v>35906200</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH42" s="3">
         <v>31164000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>34847700</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL42" s="3">
         <v>33695500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>35402900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>39160600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>42912900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>47586200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>55272300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
+        <v>1857500</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>1811600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>1681100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>658500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>1455900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>1506900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>1232700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4567,8 +4659,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4611,8 +4706,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4689,8 +4784,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4709,12 +4807,12 @@
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>6412400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4733,8 +4831,8 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4811,53 +4909,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>227135500</v>
+      </c>
+      <c r="E46" s="3">
         <v>426593000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>234611000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>420946600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>229080700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>386375800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>236438500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>458938500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>213607200</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>234404100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>432043100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>235352200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>195949600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4933,92 +5034,95 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>374493800</v>
+      </c>
+      <c r="E47" s="3">
         <v>793026600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>332921900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>786205900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>323548400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>730869900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>270877700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64230000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>277710500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>260502100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>46564800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>251074500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>279938600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>505200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T47" s="3">
         <v>460600</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V47" s="3">
         <v>446100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="3">
         <v>373300</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z47" s="3">
         <v>346700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB47" s="3">
         <v>405400</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="3">
         <v>414600</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
@@ -5031,8 +5135,8 @@
       <c r="AH47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -5055,252 +5159,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>14803500</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>12664500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>12314700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>13988100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V48" s="3">
         <v>14671500</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="3">
         <v>13735300</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="3">
         <v>13767500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB48" s="3">
         <v>15919400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="3">
         <v>17871100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3">
         <v>18738600</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3">
         <v>16245700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>16259700</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL48" s="3">
         <v>16600000</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN48" s="3">
         <v>16943000</v>
       </c>
-      <c r="AN48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP48" s="3">
         <v>17081400</v>
       </c>
-      <c r="AP48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>11585500</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>11401100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>11017900</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>10079200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>10508400</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>10383700</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>10424300</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>26867300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T49" s="3">
         <v>16031100</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V49" s="3">
         <v>15245600</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X49" s="3">
         <v>14722700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z49" s="3">
         <v>14145800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB49" s="3">
         <v>15259800</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD49" s="3">
         <v>15942700</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="3">
         <v>15455300</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH49" s="3">
         <v>13761300</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>13449100</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL49" s="3">
         <v>13022200</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN49" s="3">
         <v>13027400</v>
       </c>
-      <c r="AN49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP49" s="3">
         <v>11507400</v>
       </c>
-      <c r="AP49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5421,8 +5534,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5543,130 +5659,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37756400</v>
+      </c>
+      <c r="E52" s="3">
         <v>58762300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13776600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52981400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>33360700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58347000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13194000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>60505300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37901100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>11970800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>45628800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29945000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>47064300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13443500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
         <v>12143100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3">
         <v>9693600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3">
         <v>7727500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z52" s="3">
         <v>5218100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3">
         <v>6325000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3">
         <v>4564600</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3">
         <v>5369200</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" s="3">
         <v>4913300</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>5052300</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" s="3">
         <v>3922100</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN52" s="3">
         <v>3693800</v>
       </c>
-      <c r="AN52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP52" s="3">
         <v>4013600</v>
       </c>
-      <c r="AP52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5787,130 +5909,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1319035400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1278381900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1270621800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1260133900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1259462900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1175592700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1135116500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1207401200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1128473200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>1122755600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1089847000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1121861500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1095754200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1146067600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1171692200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1168393400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1128697900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1123493100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1094381900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1049035500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1018445400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1020517400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1059971100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1138026200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1147008900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1137254900</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="3">
         <v>1129102700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1053459500</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>1072746600</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL54" s="3">
         <v>1059241900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1057745800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1062907000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1076365200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1076861600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1106378800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5953,8 +6081,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5997,53 +6126,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>675495600</v>
+      </c>
+      <c r="E57" s="3">
         <v>664725600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>675956900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>678888100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>687254400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>637876500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>612069800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>645507300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>606969800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>608280700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>583347600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>604942100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>592217200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6119,53 +6249,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51275000</v>
+      </c>
+      <c r="E58" s="3">
         <v>25839000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>105078100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>70853800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>95277400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>73428600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>98351200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>77944000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>82293000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>113028000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>84707000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>111488000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>85076500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6241,175 +6374,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>124309400</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>41154800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>75633800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>105137700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64379400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36075500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>89000000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>82345700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>77226100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>10500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>7900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>7600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>36300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>43000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>255000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>525900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>497900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>263700</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3">
         <v>357400</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN59" s="3">
         <v>542600</v>
       </c>
-      <c r="AN59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP59" s="3">
         <v>297600</v>
       </c>
-      <c r="AP59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>851080000</v>
+      </c>
+      <c r="E60" s="3">
         <v>690564600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>822189800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>825375700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>887669500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>775684400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>746496500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>723451300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>778262800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>803654400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>668054600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>793656200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>677293600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6485,252 +6624,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>171030900</v>
+      </c>
+      <c r="E61" s="3">
         <v>187198000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>94297400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>118700400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>98517600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>99832000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>84742800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>109455800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>100563700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>78792000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>113041500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>94836800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>108345700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>110945200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>108505800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>111611800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>107289600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>116576900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>113044000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>119072000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>153364800</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>156589000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>158773700</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>143733700</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>139533000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>117873100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>114991900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>117560100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>122238900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>126602800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>143713100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>233923300</v>
+      </c>
+      <c r="E62" s="3">
         <v>336931600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>289352600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>254718100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>208732700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>238318300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>246119700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>312275800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>192279500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>179604600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253824500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>176458600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>250814000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2805500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3">
         <v>3023300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3">
         <v>2992100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3">
         <v>2425600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3">
         <v>2582700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3">
         <v>3603100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3">
         <v>4942400</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3">
         <v>4335200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5008400</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>6343800</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL62" s="3">
         <v>7700600</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN62" s="3">
         <v>9405400</v>
       </c>
-      <c r="AN62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO62" s="3">
+      <c r="AO62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP62" s="3">
         <v>7492500</v>
       </c>
-      <c r="AP62" s="3" t="s">
+      <c r="AQ62" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6851,8 +6999,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6973,8 +7124,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7095,130 +7249,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1256361900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1214694200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1206197800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1198794300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1195247300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1113834800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1077668200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1145183000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1071454700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>1062424200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1034920600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1065334000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1036453400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1088767800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1110841600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1102972300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1064558900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1056431400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1029063700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>987422100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>960700300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>962908200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>999830000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1074619600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1077126100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1072334400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF66" s="3">
         <v>1062016900</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH66" s="3">
         <v>987519000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>1010310300</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL66" s="3">
         <v>995453300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>994181600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1000472300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1010976100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1013161900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1042610600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7261,8 +7421,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7383,8 +7544,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7505,8 +7669,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7627,8 +7794,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7749,130 +7919,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>8280500</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>8467000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>7705200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>7401400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8240200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6964800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>8648800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7503700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7725200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10206400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17238400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>24896400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3">
         <v>27158200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X72" s="3">
         <v>24794700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z72" s="3">
         <v>21471100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB72" s="3">
         <v>23206500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>23104000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>25586600</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>24565400</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>23321000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>24416700</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN72" s="3">
         <v>23083700</v>
       </c>
-      <c r="AN72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP72" s="3">
         <v>24034100</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7993,8 +8169,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8115,8 +8294,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8237,130 +8419,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62375000</v>
+      </c>
+      <c r="E76" s="3">
         <v>63687700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64156100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61339600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>64004700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61757900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>57233000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61908600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>56732800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59567100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60075400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54657900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56208500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58994000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>57299800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60850700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>65421000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>64139000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67061700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>65318200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61613400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>57745100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>57609200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60141100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>63406600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>69882800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>64920500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="3">
         <v>67085800</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH76" s="3">
         <v>65940400</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>62436300</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="3">
         <v>63788600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>63564200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>62434700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>65389200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>63699700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>63768200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8481,257 +8669,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2035300</v>
+      </c>
+      <c r="E81" s="3">
         <v>2021600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1886900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>992000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1915300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1448300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>863800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1765200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1699800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1350100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1562900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1715800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1673600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1868100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1573300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T81" s="3">
         <v>2873700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V81" s="3">
         <v>2210200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X81" s="3">
         <v>4306200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1287300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-305000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD81" s="3">
         <v>705100</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="3">
         <v>2666700</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH81" s="3">
         <v>2583500</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>2747200</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL81" s="3">
         <v>2222500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1777800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1878200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1008700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>607000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8774,8 +8971,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8818,8 +9016,8 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8896,8 +9094,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9018,8 +9219,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9140,8 +9344,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9262,8 +9469,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9384,8 +9594,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9506,8 +9719,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9550,8 +9766,8 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -9559,77 +9775,80 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>8390800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>31825400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-587800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>16082800</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-20216000</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>5428500</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>1940800</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="3">
         <v>-6108100</v>
       </c>
-      <c r="AN89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP89" s="3">
         <v>-27033700</v>
       </c>
-      <c r="AP89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9672,8 +9891,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9716,86 +9936,89 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1675000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1553000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1314000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3397900</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-2149300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-2562400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-2254600</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-2336100</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-2210800</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-2556400</v>
       </c>
-      <c r="AN91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-2554600</v>
       </c>
-      <c r="AP91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9916,8 +10139,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10038,8 +10264,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10082,8 +10311,8 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -10091,77 +10320,80 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3225300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-4685200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>1513800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-4449100</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>5699200</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>9833100</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>8424500</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="3">
         <v>455200</v>
       </c>
-      <c r="AN94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP94" s="3">
         <v>1235100</v>
       </c>
-      <c r="AP94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10204,8 +10436,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10248,8 +10481,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10261,11 +10494,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1111400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10285,49 +10518,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1076000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2091400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1010400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1906900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-933900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-2045200</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-773000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10448,8 +10684,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10570,8 +10809,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10692,8 +10934,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10736,8 +10981,8 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -10745,77 +10990,80 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-4098400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-6230100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-2390700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-6599600</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-2043300</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3560400</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-2377800</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-4168600</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP100" s="3">
         <v>-6285000</v>
       </c>
-      <c r="AP100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10858,8 +11106,8 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10867,77 +11115,80 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>88700</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-229600</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3">
         <v>2600</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP101" s="3">
         <v>7900</v>
       </c>
-      <c r="AP101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10980,8 +11231,8 @@
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -10989,73 +11240,76 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>1155800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>20680500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-1471500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>5034100</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-16557400</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>11702500</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>7987600</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3">
         <v>-9821500</v>
       </c>
-      <c r="AN102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-32075700</v>
       </c>
-      <c r="AP102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
